--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/CONNECTICUT_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/CONNECTICUT_2022.xlsx
@@ -3217,7 +3217,7 @@
         <v>14</v>
       </c>
       <c r="D159">
-        <v>0.009790209790209791</v>
+        <v>0.009790209790209793</v>
       </c>
     </row>
     <row r="160">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C225">
@@ -6043,7 +6043,7 @@
         <v>14</v>
       </c>
       <c r="D316">
-        <v>0.009790209790209791</v>
+        <v>0.009790209790209793</v>
       </c>
     </row>
     <row r="317">
